--- a/output/yearly_total_coral_cover_iteration_82_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_82_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.255563456719369</v>
+        <v>1.283288011887299</v>
       </c>
       <c r="C3" t="n">
-        <v>4.59202365766108</v>
+        <v>4.645695804652253</v>
       </c>
       <c r="D3" t="n">
-        <v>6.207114680250662</v>
+        <v>6.127691290977095</v>
       </c>
       <c r="E3" t="n">
-        <v>12.05470179463111</v>
+        <v>12.05667510751665</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.387561060415997</v>
+        <v>1.453269096603348</v>
       </c>
       <c r="C4" t="n">
-        <v>5.031033102298673</v>
+        <v>5.156950295107015</v>
       </c>
       <c r="D4" t="n">
-        <v>6.479872464167378</v>
+        <v>6.363869115709117</v>
       </c>
       <c r="E4" t="n">
-        <v>12.89846662688205</v>
+        <v>12.97408850741948</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.57206175957331</v>
+        <v>1.691996957052601</v>
       </c>
       <c r="C5" t="n">
-        <v>5.590119982114103</v>
+        <v>5.81715527892446</v>
       </c>
       <c r="D5" t="n">
-        <v>6.806385312549867</v>
+        <v>6.667563084637666</v>
       </c>
       <c r="E5" t="n">
-        <v>13.96856705423728</v>
+        <v>14.17671532061473</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.790234280861993</v>
+        <v>1.969346470800482</v>
       </c>
       <c r="C6" t="n">
-        <v>6.284480972621529</v>
+        <v>6.640813457923461</v>
       </c>
       <c r="D6" t="n">
-        <v>7.162302382083999</v>
+        <v>6.941255663572132</v>
       </c>
       <c r="E6" t="n">
-        <v>15.23701763556752</v>
+        <v>15.55141559229608</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.047961812279372</v>
+        <v>2.272765675041663</v>
       </c>
       <c r="C7" t="n">
-        <v>7.175475123654881</v>
+        <v>7.611845933604251</v>
       </c>
       <c r="D7" t="n">
-        <v>7.539722986725977</v>
+        <v>7.356016325852805</v>
       </c>
       <c r="E7" t="n">
-        <v>16.76315992266023</v>
+        <v>17.24062793449872</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.302909357033391</v>
+        <v>1.453827985273054</v>
       </c>
       <c r="C8" t="n">
-        <v>4.981237275158828</v>
+        <v>5.259960474499636</v>
       </c>
       <c r="D8" t="n">
-        <v>5.798356006898062</v>
+        <v>5.653438962897536</v>
       </c>
       <c r="E8" t="n">
-        <v>12.08250263909028</v>
+        <v>12.36722742267023</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.670982641274718</v>
+        <v>1.843658546019772</v>
       </c>
       <c r="C9" t="n">
-        <v>6.233527548863205</v>
+        <v>6.436342199384244</v>
       </c>
       <c r="D9" t="n">
-        <v>6.287464818273858</v>
+        <v>6.155620820327425</v>
       </c>
       <c r="E9" t="n">
-        <v>14.19197500841178</v>
+        <v>14.43562156573144</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.085060145314638</v>
+        <v>2.269012844792928</v>
       </c>
       <c r="C10" t="n">
-        <v>7.722619986392032</v>
+        <v>7.77342346380571</v>
       </c>
       <c r="D10" t="n">
-        <v>6.831594310853032</v>
+        <v>6.759146722940231</v>
       </c>
       <c r="E10" t="n">
-        <v>16.6392744425597</v>
+        <v>16.80158303153887</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.488910487544366</v>
+        <v>2.694858473414453</v>
       </c>
       <c r="C11" t="n">
-        <v>9.324548106972362</v>
+        <v>9.193872062134087</v>
       </c>
       <c r="D11" t="n">
-        <v>7.339939842190022</v>
+        <v>7.286590660947209</v>
       </c>
       <c r="E11" t="n">
-        <v>19.15339843670675</v>
+        <v>19.17532119649575</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.893261855170666</v>
+        <v>3.119508396094159</v>
       </c>
       <c r="C12" t="n">
-        <v>10.9977245464168</v>
+        <v>10.67961555761618</v>
       </c>
       <c r="D12" t="n">
-        <v>7.874051411261916</v>
+        <v>7.80481159054992</v>
       </c>
       <c r="E12" t="n">
-        <v>21.76503781284938</v>
+        <v>21.60393554426026</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.267008010804567</v>
+        <v>3.526064527035954</v>
       </c>
       <c r="C13" t="n">
-        <v>12.68174151687898</v>
+        <v>12.16353031930531</v>
       </c>
       <c r="D13" t="n">
-        <v>8.469645114334801</v>
+        <v>8.321406239068235</v>
       </c>
       <c r="E13" t="n">
-        <v>24.41839464201835</v>
+        <v>24.0110010854095</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.85060423998228</v>
+        <v>2.020171703459789</v>
       </c>
       <c r="C14" t="n">
-        <v>8.740912144945137</v>
+        <v>8.516249000305296</v>
       </c>
       <c r="D14" t="n">
-        <v>6.419265356465237</v>
+        <v>6.345869898095746</v>
       </c>
       <c r="E14" t="n">
-        <v>17.01078174139266</v>
+        <v>16.88229060186083</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.912886314339698</v>
+        <v>2.090003417662865</v>
       </c>
       <c r="C15" t="n">
-        <v>9.54088926175065</v>
+        <v>9.106652434685243</v>
       </c>
       <c r="D15" t="n">
-        <v>6.468558908695469</v>
+        <v>6.386013561722398</v>
       </c>
       <c r="E15" t="n">
-        <v>17.92233448478582</v>
+        <v>17.58266941407051</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.218710541689622</v>
+        <v>2.445101562288936</v>
       </c>
       <c r="C16" t="n">
-        <v>11.27993751009936</v>
+        <v>10.65585031198671</v>
       </c>
       <c r="D16" t="n">
-        <v>6.986450457639748</v>
+        <v>6.975572693076692</v>
       </c>
       <c r="E16" t="n">
-        <v>20.48509850942873</v>
+        <v>20.07652456735234</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.781175042337946</v>
+        <v>1.974648062413865</v>
       </c>
       <c r="C17" t="n">
-        <v>10.41334881156071</v>
+        <v>9.713343063478645</v>
       </c>
       <c r="D17" t="n">
-        <v>6.517518666706257</v>
+        <v>6.518431692071206</v>
       </c>
       <c r="E17" t="n">
-        <v>18.71204252060491</v>
+        <v>18.20642281796372</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.02633707904246</v>
+        <v>2.273747317989698</v>
       </c>
       <c r="C18" t="n">
-        <v>12.11012300376455</v>
+        <v>11.21040032020756</v>
       </c>
       <c r="D18" t="n">
-        <v>6.952373994825339</v>
+        <v>6.972156211065914</v>
       </c>
       <c r="E18" t="n">
-        <v>21.08883407763235</v>
+        <v>20.45630384926318</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.0231562164807</v>
+        <v>2.304191314298392</v>
       </c>
       <c r="C19" t="n">
-        <v>12.92544483718745</v>
+        <v>11.88591146306867</v>
       </c>
       <c r="D19" t="n">
-        <v>7.050342598232129</v>
+        <v>7.103052632473141</v>
       </c>
       <c r="E19" t="n">
-        <v>21.99894365190027</v>
+        <v>21.2931554098402</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.243018614846773</v>
+        <v>2.587101550231195</v>
       </c>
       <c r="C20" t="n">
-        <v>14.80463757031739</v>
+        <v>13.53920404945142</v>
       </c>
       <c r="D20" t="n">
-        <v>7.570649246528854</v>
+        <v>7.58196879755882</v>
       </c>
       <c r="E20" t="n">
-        <v>24.61830543169302</v>
+        <v>23.70827439724144</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.325035423990793</v>
+        <v>1.551122102801791</v>
       </c>
       <c r="C21" t="n">
-        <v>10.77983522955604</v>
+        <v>9.862077840672036</v>
       </c>
       <c r="D21" t="n">
-        <v>6.345752088371236</v>
+        <v>6.36355117424923</v>
       </c>
       <c r="E21" t="n">
-        <v>18.45062274191807</v>
+        <v>17.77675111772306</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_82_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_82_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.283288011887299</v>
+        <v>1.262416055695012</v>
       </c>
       <c r="C3" t="n">
-        <v>4.645695804652253</v>
+        <v>4.687429899559785</v>
       </c>
       <c r="D3" t="n">
-        <v>6.127691290977095</v>
+        <v>6.048042099731552</v>
       </c>
       <c r="E3" t="n">
-        <v>12.05667510751665</v>
+        <v>11.99788805498635</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.453269096603348</v>
+        <v>1.399557933620399</v>
       </c>
       <c r="C4" t="n">
-        <v>5.156950295107015</v>
+        <v>5.28318705424067</v>
       </c>
       <c r="D4" t="n">
-        <v>6.363869115709117</v>
+        <v>6.287058360198663</v>
       </c>
       <c r="E4" t="n">
-        <v>12.97408850741948</v>
+        <v>12.96980334805973</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.691996957052601</v>
+        <v>1.592509179677851</v>
       </c>
       <c r="C5" t="n">
-        <v>5.81715527892446</v>
+        <v>6.082728041733093</v>
       </c>
       <c r="D5" t="n">
-        <v>6.667563084637666</v>
+        <v>6.511939039076391</v>
       </c>
       <c r="E5" t="n">
-        <v>14.17671532061473</v>
+        <v>14.18717626048733</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.969346470800482</v>
+        <v>1.823656550535707</v>
       </c>
       <c r="C6" t="n">
-        <v>6.640813457923461</v>
+        <v>7.035132365782112</v>
       </c>
       <c r="D6" t="n">
-        <v>6.941255663572132</v>
+        <v>6.768657413819124</v>
       </c>
       <c r="E6" t="n">
-        <v>15.55141559229608</v>
+        <v>15.62744633013694</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.272765675041663</v>
+        <v>2.083707336650283</v>
       </c>
       <c r="C7" t="n">
-        <v>7.611845933604251</v>
+        <v>8.089808673185832</v>
       </c>
       <c r="D7" t="n">
-        <v>7.356016325852805</v>
+        <v>7.083128672985506</v>
       </c>
       <c r="E7" t="n">
-        <v>17.24062793449872</v>
+        <v>17.25664468282162</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.453827985273054</v>
+        <v>1.304747172321641</v>
       </c>
       <c r="C8" t="n">
-        <v>5.259960474499636</v>
+        <v>5.603568777355526</v>
       </c>
       <c r="D8" t="n">
-        <v>5.653438962897536</v>
+        <v>5.289955177838738</v>
       </c>
       <c r="E8" t="n">
-        <v>12.36722742267023</v>
+        <v>12.19827112751591</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.843658546019772</v>
+        <v>1.643090432033886</v>
       </c>
       <c r="C9" t="n">
-        <v>6.436342199384244</v>
+        <v>6.7702802107274</v>
       </c>
       <c r="D9" t="n">
-        <v>6.155620820327425</v>
+        <v>5.779729011449949</v>
       </c>
       <c r="E9" t="n">
-        <v>14.43562156573144</v>
+        <v>14.19309965421123</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.269012844792928</v>
+        <v>2.00333657899084</v>
       </c>
       <c r="C10" t="n">
-        <v>7.77342346380571</v>
+        <v>8.02533259415828</v>
       </c>
       <c r="D10" t="n">
-        <v>6.759146722940231</v>
+        <v>6.220236034775173</v>
       </c>
       <c r="E10" t="n">
-        <v>16.80158303153887</v>
+        <v>16.2489052079243</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.694858473414453</v>
+        <v>2.370636978470527</v>
       </c>
       <c r="C11" t="n">
-        <v>9.193872062134087</v>
+        <v>9.371624762945833</v>
       </c>
       <c r="D11" t="n">
-        <v>7.286590660947209</v>
+        <v>6.628466954311902</v>
       </c>
       <c r="E11" t="n">
-        <v>19.17532119649575</v>
+        <v>18.37072869572826</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.119508396094159</v>
+        <v>2.742031824185502</v>
       </c>
       <c r="C12" t="n">
-        <v>10.67961555761618</v>
+        <v>10.77098741538502</v>
       </c>
       <c r="D12" t="n">
-        <v>7.80481159054992</v>
+        <v>7.024846135508716</v>
       </c>
       <c r="E12" t="n">
-        <v>21.60393554426026</v>
+        <v>20.53786537507924</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.526064527035954</v>
+        <v>3.102301247672336</v>
       </c>
       <c r="C13" t="n">
-        <v>12.16353031930531</v>
+        <v>12.20105485511858</v>
       </c>
       <c r="D13" t="n">
-        <v>8.321406239068235</v>
+        <v>7.455598358945556</v>
       </c>
       <c r="E13" t="n">
-        <v>24.0110010854095</v>
+        <v>22.75895446173647</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.020171703459789</v>
+        <v>1.789205738558685</v>
       </c>
       <c r="C14" t="n">
-        <v>8.516249000305296</v>
+        <v>8.694779820322578</v>
       </c>
       <c r="D14" t="n">
-        <v>6.345869898095746</v>
+        <v>5.701077640900526</v>
       </c>
       <c r="E14" t="n">
-        <v>16.88229060186083</v>
+        <v>16.18506319978179</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.090003417662865</v>
+        <v>1.841768510644059</v>
       </c>
       <c r="C15" t="n">
-        <v>9.106652434685243</v>
+        <v>9.152892751555267</v>
       </c>
       <c r="D15" t="n">
-        <v>6.386013561722398</v>
+        <v>5.667855298588814</v>
       </c>
       <c r="E15" t="n">
-        <v>17.58266941407051</v>
+        <v>16.66251656078814</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.445101562288936</v>
+        <v>2.154730043803857</v>
       </c>
       <c r="C16" t="n">
-        <v>10.65585031198671</v>
+        <v>10.67999148803414</v>
       </c>
       <c r="D16" t="n">
-        <v>6.975572693076692</v>
+        <v>6.084067237804248</v>
       </c>
       <c r="E16" t="n">
-        <v>20.07652456735234</v>
+        <v>18.91878876964224</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.974648062413865</v>
+        <v>1.740255798024938</v>
       </c>
       <c r="C17" t="n">
-        <v>9.713343063478645</v>
+        <v>9.675310157416124</v>
       </c>
       <c r="D17" t="n">
-        <v>6.518431692071206</v>
+        <v>5.626543355194108</v>
       </c>
       <c r="E17" t="n">
-        <v>18.20642281796372</v>
+        <v>17.04210931063517</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.273747317989698</v>
+        <v>2.010953092516912</v>
       </c>
       <c r="C18" t="n">
-        <v>11.21040032020756</v>
+        <v>11.25713151092971</v>
       </c>
       <c r="D18" t="n">
-        <v>6.972156211065914</v>
+        <v>5.994600569516236</v>
       </c>
       <c r="E18" t="n">
-        <v>20.45630384926318</v>
+        <v>19.26268517296286</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.304191314298392</v>
+        <v>2.044371784369473</v>
       </c>
       <c r="C19" t="n">
-        <v>11.88591146306867</v>
+        <v>12.03632502883632</v>
       </c>
       <c r="D19" t="n">
-        <v>7.103052632473141</v>
+        <v>6.060171498682881</v>
       </c>
       <c r="E19" t="n">
-        <v>21.2931554098402</v>
+        <v>20.14086831188867</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.587101550231195</v>
+        <v>2.296170435554695</v>
       </c>
       <c r="C20" t="n">
-        <v>13.53920404945142</v>
+        <v>13.863210244284</v>
       </c>
       <c r="D20" t="n">
-        <v>7.58196879755882</v>
+        <v>6.421621550955428</v>
       </c>
       <c r="E20" t="n">
-        <v>23.70827439724144</v>
+        <v>22.58100223079412</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.551122102801791</v>
+        <v>1.37808906992829</v>
       </c>
       <c r="C21" t="n">
-        <v>9.862077840672036</v>
+        <v>10.30111541401121</v>
       </c>
       <c r="D21" t="n">
-        <v>6.36355117424923</v>
+        <v>5.332500100295145</v>
       </c>
       <c r="E21" t="n">
-        <v>17.77675111772306</v>
+        <v>17.01170458423465</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_82_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_82_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.262416055695012</v>
+        <v>2.590762991051565</v>
       </c>
       <c r="C3" t="n">
-        <v>4.687429899559785</v>
+        <v>7.734460837815981</v>
       </c>
       <c r="D3" t="n">
-        <v>6.048042099731552</v>
+        <v>8.221594866887122</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99788805498635</v>
+        <v>18.54681869575467</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.399557933620399</v>
+        <v>1.069049327502621</v>
       </c>
       <c r="C4" t="n">
-        <v>5.28318705424067</v>
+        <v>4.545592804105612</v>
       </c>
       <c r="D4" t="n">
-        <v>6.287058360198663</v>
+        <v>5.832189700130495</v>
       </c>
       <c r="E4" t="n">
-        <v>12.96980334805973</v>
+        <v>11.44683183173873</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.592509179677851</v>
+        <v>1.158846884138276</v>
       </c>
       <c r="C5" t="n">
-        <v>6.082728041733093</v>
+        <v>5.231254791928803</v>
       </c>
       <c r="D5" t="n">
-        <v>6.511939039076391</v>
+        <v>6.110524962290626</v>
       </c>
       <c r="E5" t="n">
-        <v>14.18717626048733</v>
+        <v>12.5006266383577</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.823656550535707</v>
+        <v>1.260344765345316</v>
       </c>
       <c r="C6" t="n">
-        <v>7.035132365782112</v>
+        <v>6.120498991690962</v>
       </c>
       <c r="D6" t="n">
-        <v>6.768657413819124</v>
+        <v>6.395905755686749</v>
       </c>
       <c r="E6" t="n">
-        <v>15.62744633013694</v>
+        <v>13.77674951272303</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.083707336650283</v>
+        <v>1.36507079008373</v>
       </c>
       <c r="C7" t="n">
-        <v>8.089808673185832</v>
+        <v>7.165925444294662</v>
       </c>
       <c r="D7" t="n">
-        <v>7.083128672985506</v>
+        <v>6.707139037836196</v>
       </c>
       <c r="E7" t="n">
-        <v>17.25664468282162</v>
+        <v>15.23813527221459</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.304747172321641</v>
+        <v>1.477384212950586</v>
       </c>
       <c r="C8" t="n">
-        <v>5.603568777355526</v>
+        <v>8.4077005872103</v>
       </c>
       <c r="D8" t="n">
-        <v>5.289955177838738</v>
+        <v>7.031952304416019</v>
       </c>
       <c r="E8" t="n">
-        <v>12.19827112751591</v>
+        <v>16.91703710457691</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.643090432033886</v>
+        <v>1.572193664177602</v>
       </c>
       <c r="C9" t="n">
-        <v>6.7702802107274</v>
+        <v>9.820372257912419</v>
       </c>
       <c r="D9" t="n">
-        <v>5.779729011449949</v>
+        <v>7.434994288944241</v>
       </c>
       <c r="E9" t="n">
-        <v>14.19309965421123</v>
+        <v>18.82756021103426</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.00333657899084</v>
+        <v>0.9899354801002288</v>
       </c>
       <c r="C10" t="n">
-        <v>8.02533259415828</v>
+        <v>7.245543494267522</v>
       </c>
       <c r="D10" t="n">
-        <v>6.220236034775173</v>
+        <v>5.832386396343536</v>
       </c>
       <c r="E10" t="n">
-        <v>16.2489052079243</v>
+        <v>14.06786537071129</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.370636978470527</v>
+        <v>0.9073312282649022</v>
       </c>
       <c r="C11" t="n">
-        <v>9.371624762945833</v>
+        <v>7.854344880625054</v>
       </c>
       <c r="D11" t="n">
-        <v>6.628466954311902</v>
+        <v>5.657645122464646</v>
       </c>
       <c r="E11" t="n">
-        <v>18.37072869572826</v>
+        <v>14.4193212313546</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.742031824185502</v>
+        <v>0.9686806423032854</v>
       </c>
       <c r="C12" t="n">
-        <v>10.77098741538502</v>
+        <v>9.430717534380074</v>
       </c>
       <c r="D12" t="n">
-        <v>7.024846135508716</v>
+        <v>5.978156295470102</v>
       </c>
       <c r="E12" t="n">
-        <v>20.53786537507924</v>
+        <v>16.37755447215346</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.102301247672336</v>
+        <v>0.7622289175772237</v>
       </c>
       <c r="C13" t="n">
-        <v>12.20105485511858</v>
+        <v>9.100614686304125</v>
       </c>
       <c r="D13" t="n">
-        <v>7.455598358945556</v>
+        <v>5.400967185189318</v>
       </c>
       <c r="E13" t="n">
-        <v>22.75895446173647</v>
+        <v>15.26381078907067</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.789205738558685</v>
+        <v>0.8245698967968962</v>
       </c>
       <c r="C14" t="n">
-        <v>8.694779820322578</v>
+        <v>10.78428254665628</v>
       </c>
       <c r="D14" t="n">
-        <v>5.701077640900526</v>
+        <v>5.701951396357305</v>
       </c>
       <c r="E14" t="n">
-        <v>16.18506319978179</v>
+        <v>17.31080383981048</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.841768510644059</v>
+        <v>0.7988284719915447</v>
       </c>
       <c r="C15" t="n">
-        <v>9.152892751555267</v>
+        <v>11.7420363370113</v>
       </c>
       <c r="D15" t="n">
-        <v>5.667855298588814</v>
+        <v>5.707910604922083</v>
       </c>
       <c r="E15" t="n">
-        <v>16.66251656078814</v>
+        <v>18.24877541392492</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.154730043803857</v>
+        <v>0.8707022214194536</v>
       </c>
       <c r="C16" t="n">
-        <v>10.67999148803414</v>
+        <v>13.74129681437063</v>
       </c>
       <c r="D16" t="n">
-        <v>6.084067237804248</v>
+        <v>6.109317788757477</v>
       </c>
       <c r="E16" t="n">
-        <v>18.91878876964224</v>
+        <v>20.72131682454756</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.740255798024938</v>
+        <v>0.5262560393844603</v>
       </c>
       <c r="C17" t="n">
-        <v>9.675310157416124</v>
+        <v>10.26337703225996</v>
       </c>
       <c r="D17" t="n">
-        <v>5.626543355194108</v>
+        <v>5.052868901694526</v>
       </c>
       <c r="E17" t="n">
-        <v>17.04210931063517</v>
+        <v>15.84250197333895</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.010953092516912</v>
+        <v>0.4138950146334128</v>
       </c>
       <c r="C18" t="n">
-        <v>11.25713151092971</v>
+        <v>9.223696395985549</v>
       </c>
       <c r="D18" t="n">
-        <v>5.994600569516236</v>
+        <v>4.568219330016046</v>
       </c>
       <c r="E18" t="n">
-        <v>19.26268517296286</v>
+        <v>14.20581074063501</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.044371784369473</v>
+        <v>0.4842077852115694</v>
       </c>
       <c r="C19" t="n">
-        <v>12.03632502883632</v>
+        <v>11.46115831882628</v>
       </c>
       <c r="D19" t="n">
-        <v>6.060171498682881</v>
+        <v>5.048549211795841</v>
       </c>
       <c r="E19" t="n">
-        <v>20.14086831188867</v>
+        <v>16.99391531583369</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.296170435554695</v>
+        <v>0.546322962459265</v>
       </c>
       <c r="C20" t="n">
-        <v>13.863210244284</v>
+        <v>13.83239318384769</v>
       </c>
       <c r="D20" t="n">
-        <v>6.421621550955428</v>
+        <v>5.488480175545878</v>
       </c>
       <c r="E20" t="n">
-        <v>22.58100223079412</v>
+        <v>19.86719632185283</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.37808906992829</v>
+        <v>0.5975603751439061</v>
       </c>
       <c r="C21" t="n">
-        <v>10.30111541401121</v>
+        <v>16.20957743995683</v>
       </c>
       <c r="D21" t="n">
-        <v>5.332500100295145</v>
+        <v>5.885214240309057</v>
       </c>
       <c r="E21" t="n">
-        <v>17.01170458423465</v>
+        <v>22.6923520554098</v>
       </c>
     </row>
   </sheetData>
